--- a/testakten/erbstreit-krypto-multisig-edelmann-stuttgart/xlsx/nachlassverzeichnis_aktiv_passiv.xlsx
+++ b/testakten/erbstreit-krypto-multisig-edelmann-stuttgart/xlsx/nachlassverzeichnis_aktiv_passiv.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>SV Bender &amp; Moerser 02.05.2025; Gegengutachten Klever ausstehend</t>
+          <t>SV Bender &amp; Mörser 02.05.2025; Gegengutachten Klever ausstehend</t>
         </is>
       </c>
     </row>
